--- a/Formato-archivos.xlsx
+++ b/Formato-archivos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Documentos Mari\Maestría en mecatrónica EU4M\Segundo Semestre\Proyecto mecatronico\Primer diseño preliminar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Documentos Mari\Maestría en mecatrónica EU4M\Segundo Semestre\Proyecto mecatronico\Diseño final\RoboticArmEU4M\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CE1675-4C40-4C08-879E-AE533222B069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A118839A-B607-4790-B5C4-9F07B16483BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" activeTab="1" xr2:uid="{8A9B17CD-70AD-419F-A450-4EA25489036B}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="121">
   <si>
     <t>Ensamble</t>
   </si>
@@ -400,6 +400,9 @@
   </si>
   <si>
     <t>InsertoM4-2040617</t>
+  </si>
+  <si>
+    <t>Plano</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1084,7 @@
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="16.7109375" customWidth="1"/>
     <col min="4" max="4" width="32.85546875" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="47.28515625" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="9" width="40.85546875" customWidth="1"/>
@@ -1113,6 +1116,9 @@
       <c r="D3" s="11" t="s">
         <v>25</v>
       </c>
+      <c r="E3" s="11" t="s">
+        <v>120</v>
+      </c>
       <c r="H3" s="3"/>
       <c r="I3" s="5"/>
     </row>

--- a/Formato-archivos.xlsx
+++ b/Formato-archivos.xlsx
@@ -5,21 +5,21 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Documentos Mari\Maestría en mecatrónica EU4M\Segundo Semestre\Proyecto mecatronico\Diseño final\RoboticArmEU4M\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Master\ProyectoRobot_Github\RoboticArmEU4M\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A118839A-B607-4790-B5C4-9F07B16483BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A64C45D-352F-49DE-8009-45E1232E9F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" activeTab="1" xr2:uid="{8A9B17CD-70AD-419F-A450-4EA25489036B}"/>
+    <workbookView xWindow="-16090" yWindow="14660" windowWidth="16180" windowHeight="12530" activeTab="1" xr2:uid="{8A9B17CD-70AD-419F-A450-4EA25489036B}"/>
   </bookViews>
   <sheets>
     <sheet name="Nomenclatura" sheetId="2" r:id="rId1"/>
     <sheet name="Listado de piezas" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Listado de piezas'!$A$3:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Listado de piezas'!$A$3:$D$49</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -409,7 +409,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -838,15 +838,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16FF2997-2957-4238-9165-6D201327FBA6}">
   <dimension ref="A2:N34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="1"/>
-    <col min="11" max="11" width="16.28515625" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="1"/>
+    <col min="3" max="3" width="22.84375" customWidth="1"/>
+    <col min="8" max="8" width="11.3828125" style="1"/>
+    <col min="11" max="11" width="16.3046875" customWidth="1"/>
+    <col min="14" max="14" width="11.3828125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -854,7 +854,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
@@ -865,7 +865,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>22</v>
       </c>
@@ -876,7 +876,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>26</v>
       </c>
@@ -889,7 +889,7 @@
       <c r="H6"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
         <v>26</v>
       </c>
@@ -902,7 +902,7 @@
       <c r="H7" s="3"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
         <v>28</v>
       </c>
@@ -915,7 +915,7 @@
       <c r="H8" s="3"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
         <v>28</v>
       </c>
@@ -928,7 +928,7 @@
       <c r="H9" s="3"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
         <v>28</v>
       </c>
@@ -941,7 +941,7 @@
       <c r="H10" s="3"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
         <v>28</v>
       </c>
@@ -954,7 +954,7 @@
       <c r="H11" s="3"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
         <v>28</v>
       </c>
@@ -966,7 +966,7 @@
       </c>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
         <v>28</v>
       </c>
@@ -978,35 +978,35 @@
       </c>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
-    <row r="20" spans="3:4">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="3:4">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C21" s="3"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="3:4">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C22" s="3"/>
       <c r="D22" s="4"/>
     </row>
-    <row r="23" spans="3:4">
+    <row r="23" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C23" s="3"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="3:4">
+    <row r="24" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C24" s="3"/>
       <c r="D24" s="4"/>
     </row>
-    <row r="27" spans="3:4">
+    <row r="27" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C27" s="2" t="s">
         <v>8</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="3:4">
+    <row r="28" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C28" s="3" t="s">
         <v>9</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="3:4">
+    <row r="29" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C29" s="3" t="s">
         <v>2</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="3:4">
+    <row r="30" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C30" s="3" t="s">
         <v>1</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="3:4">
+    <row r="31" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C31" s="3" t="s">
         <v>3</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="3:4">
+    <row r="32" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C32" s="3" t="s">
         <v>14</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="3:4">
+    <row r="33" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C33" s="3" t="s">
         <v>16</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="3:4">
+    <row r="34" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C34" s="3" t="s">
         <v>18</v>
       </c>
@@ -1078,32 +1078,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9199B10-773A-4EB7-9A88-ECF4D3CC318B}">
   <dimension ref="A1:M52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.84375" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="32.85546875" customWidth="1"/>
+    <col min="3" max="3" width="16.69140625" customWidth="1"/>
+    <col min="4" max="4" width="32.84375" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="47.28515625" customWidth="1"/>
+    <col min="6" max="6" width="47.3046875" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="40.85546875" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" style="1"/>
+    <col min="9" max="9" width="40.84375" customWidth="1"/>
+    <col min="13" max="13" width="11.3828125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="E2" s="3"/>
       <c r="F2" s="5"/>
       <c r="H2" s="3"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -1122,7 +1122,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -1136,7 +1136,7 @@
       <c r="H4" s="3"/>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
@@ -1150,7 +1150,7 @@
       <c r="H5" s="3"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
         <v>32</v>
       </c>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="D6" s="5"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
         <v>33</v>
       </c>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D7" s="5"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
         <v>34</v>
       </c>
@@ -1185,7 +1185,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
         <v>35</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
         <v>44</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
         <v>46</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
         <v>52</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
         <v>54</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
         <v>55</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
         <v>56</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
         <v>57</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
         <v>63</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
         <v>64</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
         <v>65</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25" s="3" t="s">
         <v>66</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
         <v>70</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
         <v>72</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
         <v>74</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
         <v>76</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
         <v>78</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" s="3" t="s">
         <v>80</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32" s="3" t="s">
         <v>84</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" s="3" t="s">
         <v>87</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" s="3" t="s">
         <v>88</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35" s="3" t="s">
         <v>89</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36" s="3" t="s">
         <v>90</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37" s="3" t="s">
         <v>103</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38" s="3" t="s">
         <v>104</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39" s="3" t="s">
         <v>105</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40" s="3" t="s">
         <v>106</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A41" s="3" t="s">
         <v>107</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A42" s="3" t="s">
         <v>108</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A43" s="3" t="s">
         <v>109</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A44" s="3" t="s">
         <v>110</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A45" s="3" t="s">
         <v>111</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A46" s="3" t="s">
         <v>112</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A47" s="3" t="s">
         <v>113</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A48" s="3" t="s">
         <v>116</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" s="3" t="s">
         <v>118</v>
       </c>
@@ -1756,17 +1756,17 @@
         <v>119</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="1"/>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="1"/>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B52" s="3" t="s">
         <v>1</v>
       </c>
@@ -1781,7 +1781,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D16" xr:uid="{E9199B10-773A-4EB7-9A88-ECF4D3CC318B}"/>
+  <autoFilter ref="A3:D49" xr:uid="{E9199B10-773A-4EB7-9A88-ECF4D3CC318B}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
